--- a/data/KYN_KSRA/upne_signals.xlsx
+++ b/data/KYN_KSRA/upne_signals.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -546,6 +546,18 @@
       <c r="V2">
         <v>1</v>
       </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -620,6 +632,12 @@
       <c r="X3" t="str">
         <v>Book shows one right arm on top of vertical stem</v>
       </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -688,8 +706,17 @@
       <c r="V4">
         <v>1</v>
       </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
       <c r="Y4">
         <v>120.666</v>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -759,6 +786,12 @@
       <c r="V5">
         <v>1</v>
       </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
       <c r="Y5">
         <v>119.096</v>
       </c>
@@ -770,6 +803,12 @@
       <c r="A6" t="str">
         <v>KSRA IBS DIST</v>
       </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
       <c r="D6" t="str">
         <v>KYN-KSRA</v>
       </c>
@@ -826,6 +865,12 @@
       </c>
       <c r="V6">
         <v>1</v>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
       </c>
       <c r="Y6">
         <v>118.1</v>
@@ -838,6 +883,12 @@
       <c r="A7" t="str">
         <v>KSRA S-1</v>
       </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
       <c r="D7" t="str">
         <v>KYN-KSRA</v>
       </c>
@@ -894,6 +945,12 @@
       </c>
       <c r="V7">
         <v>1</v>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
       </c>
       <c r="Y7">
         <v>116.89</v>
@@ -969,6 +1026,12 @@
       <c r="V8">
         <v>1</v>
       </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
       <c r="Y8">
         <v>115.78</v>
       </c>
@@ -1043,6 +1106,12 @@
       <c r="V9">
         <v>1</v>
       </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
       <c r="Y9">
         <v>113.23</v>
       </c>
@@ -1054,6 +1123,12 @@
       <c r="A10" t="str">
         <v>OMB IBS DIST</v>
       </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
       <c r="D10" t="str">
         <v>KYN-KSRA</v>
       </c>
@@ -1110,6 +1185,12 @@
       </c>
       <c r="V10">
         <v>1</v>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
       </c>
       <c r="Y10">
         <v>112.15</v>
@@ -1122,6 +1203,12 @@
       <c r="A11" t="str">
         <v>OMB S-6</v>
       </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
       <c r="D11" t="str">
         <v>KYN-KSRA</v>
       </c>
@@ -1178,6 +1265,12 @@
       </c>
       <c r="V11">
         <v>1</v>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
       </c>
       <c r="Y11">
         <v>109.96000000000001</v>
@@ -1253,6 +1346,12 @@
       <c r="V12">
         <v>1</v>
       </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
       <c r="Y12">
         <v>108.95</v>
       </c>
@@ -1407,13 +1506,22 @@
       <c r="V14">
         <v>1</v>
       </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
       <c r="Y14">
         <v>107.32300000000001</v>
       </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>KE S-17</v>
+        <v>KE S-19</v>
       </c>
       <c r="B15" t="str">
         <v>KE</v>
@@ -1431,19 +1539,19 @@
         <v>UP</v>
       </c>
       <c r="G15" t="str">
-        <v>106/13</v>
+        <v>UP LOOP STR</v>
       </c>
       <c r="H15" t="str">
         <v>Manual</v>
       </c>
       <c r="I15" t="str">
-        <v>Advanced Starter</v>
+        <v>Starter (Loop)</v>
       </c>
       <c r="J15" t="str">
         <v>Left</v>
       </c>
       <c r="K15" t="str">
-        <v>Left</v>
+        <v/>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1472,22 +1580,34 @@
       <c r="T15">
         <v>0</v>
       </c>
-      <c r="U15">
-        <v>400</v>
+      <c r="U15" t="str">
+        <v/>
       </c>
       <c r="V15">
         <v>1</v>
       </c>
-      <c r="Y15">
-        <v>106.083</v>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
       </c>
       <c r="Z15" t="str">
-        <v>106/13</v>
+        <v>106/39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>KE IBS DIST</v>
+        <v>KE S-17</v>
+      </c>
+      <c r="B16" t="str">
+        <v>KE</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Khardi</v>
       </c>
       <c r="D16" t="str">
         <v>KYN-KSRA</v>
@@ -1499,19 +1619,19 @@
         <v>UP</v>
       </c>
       <c r="G16" t="str">
-        <v>105/17</v>
+        <v>106/13</v>
       </c>
       <c r="H16" t="str">
         <v>Manual</v>
       </c>
       <c r="I16" t="str">
-        <v>IBS Distant</v>
+        <v>Advanced Starter</v>
       </c>
       <c r="J16" t="str">
         <v>Left</v>
       </c>
       <c r="K16" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1541,21 +1661,33 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="V16">
         <v>1</v>
       </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
       <c r="Y16">
-        <v>105.003</v>
+        <v>106.083</v>
       </c>
       <c r="Z16" t="str">
-        <v>105/17</v>
+        <v>106/13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>KE S-16</v>
+        <v>KE IBS DIST</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
       </c>
       <c r="D17" t="str">
         <v>KYN-KSRA</v>
@@ -1567,19 +1699,19 @@
         <v>UP</v>
       </c>
       <c r="G17" t="str">
-        <v>104/15</v>
+        <v>105/17</v>
       </c>
       <c r="H17" t="str">
-        <v>IBS</v>
+        <v>Manual</v>
       </c>
       <c r="I17" t="str">
-        <v>IBS</v>
+        <v>IBS Distant</v>
       </c>
       <c r="J17" t="str">
         <v>Left</v>
       </c>
       <c r="K17" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1609,27 +1741,33 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="V17">
         <v>1</v>
       </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
       <c r="Y17">
-        <v>103.673</v>
+        <v>105.003</v>
       </c>
       <c r="Z17" t="str">
-        <v>104/15</v>
+        <v>105/17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>THS DIST</v>
+        <v>KE S-16</v>
       </c>
       <c r="B18" t="str">
-        <v>THS</v>
+        <v/>
       </c>
       <c r="C18" t="str">
-        <v>Thansit</v>
+        <v/>
       </c>
       <c r="D18" t="str">
         <v>KYN-KSRA</v>
@@ -1641,19 +1779,19 @@
         <v>UP</v>
       </c>
       <c r="G18" t="str">
-        <v>102/07</v>
+        <v>104/15</v>
       </c>
       <c r="H18" t="str">
-        <v>Manual</v>
+        <v>IBS</v>
       </c>
       <c r="I18" t="str">
-        <v>Distant</v>
+        <v>IBS</v>
       </c>
       <c r="J18" t="str">
         <v>Left</v>
       </c>
       <c r="K18" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1683,21 +1821,27 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V18">
         <v>1</v>
       </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
       <c r="Y18">
-        <v>102.68</v>
+        <v>103.673</v>
       </c>
       <c r="Z18" t="str">
-        <v>102/07</v>
+        <v>104/15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>THS S-9</v>
+        <v>THS DIST</v>
       </c>
       <c r="B19" t="str">
         <v>THS</v>
@@ -1715,19 +1859,19 @@
         <v>UP</v>
       </c>
       <c r="G19" t="str">
-        <v>100/33</v>
+        <v>102/07</v>
       </c>
       <c r="H19" t="str">
         <v>Manual</v>
       </c>
       <c r="I19" t="str">
-        <v>Home</v>
+        <v>Distant</v>
       </c>
       <c r="J19" t="str">
         <v>Left</v>
       </c>
       <c r="K19" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1757,21 +1901,33 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="V19">
         <v>1</v>
       </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
       <c r="Y19">
-        <v>101.03</v>
+        <v>102.68</v>
       </c>
       <c r="Z19" t="str">
-        <v>100/33</v>
+        <v>102/07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>THS IBS DIST</v>
+        <v>THS S-9</v>
+      </c>
+      <c r="B20" t="str">
+        <v>THS</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Thansit</v>
       </c>
       <c r="D20" t="str">
         <v>KYN-KSRA</v>
@@ -1783,19 +1939,19 @@
         <v>UP</v>
       </c>
       <c r="G20" t="str">
-        <v>99/7</v>
+        <v>100/33</v>
       </c>
       <c r="H20" t="str">
         <v>Manual</v>
       </c>
       <c r="I20" t="str">
-        <v>IBS Distant</v>
+        <v>Home</v>
       </c>
       <c r="J20" t="str">
         <v>Left</v>
       </c>
       <c r="K20" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1825,21 +1981,33 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="V20">
         <v>1</v>
       </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
       <c r="Y20">
-        <v>99.88</v>
+        <v>101.03</v>
       </c>
       <c r="Z20" t="str">
-        <v>99/7</v>
+        <v>100/33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>THS S-6</v>
+        <v>THS IBS DIST</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
       </c>
       <c r="D21" t="str">
         <v>KYN-KSRA</v>
@@ -1851,13 +2019,13 @@
         <v>UP</v>
       </c>
       <c r="G21" t="str">
-        <v>98/9</v>
+        <v>99/7</v>
       </c>
       <c r="H21" t="str">
-        <v>IBS</v>
+        <v>Manual</v>
       </c>
       <c r="I21" t="str">
-        <v>IBS</v>
+        <v>IBS Distant</v>
       </c>
       <c r="J21" t="str">
         <v>Left</v>
@@ -1893,27 +2061,33 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="V21">
         <v>1</v>
       </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
       <c r="Y21">
-        <v>97.94</v>
+        <v>99.88</v>
       </c>
       <c r="Z21" t="str">
-        <v>98/9</v>
+        <v>99/7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ATG DIST</v>
+        <v>THS S-6</v>
       </c>
       <c r="B22" t="str">
-        <v>ATG</v>
+        <v/>
       </c>
       <c r="C22" t="str">
-        <v>Atgaon</v>
+        <v/>
       </c>
       <c r="D22" t="str">
         <v>KYN-KSRA</v>
@@ -1925,13 +2099,13 @@
         <v>UP</v>
       </c>
       <c r="G22" t="str">
-        <v>97/3</v>
+        <v>98/9</v>
       </c>
       <c r="H22" t="str">
-        <v>Manual</v>
+        <v>IBS</v>
       </c>
       <c r="I22" t="str">
-        <v>Distant</v>
+        <v>IBS</v>
       </c>
       <c r="J22" t="str">
         <v>Left</v>
@@ -1967,21 +2141,27 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="V22">
         <v>1</v>
       </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
       <c r="Y22">
-        <v>96.36</v>
+        <v>97.94</v>
       </c>
       <c r="Z22" t="str">
-        <v>97/3</v>
+        <v>98/9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ATG S-27</v>
+        <v>ATG DIST</v>
       </c>
       <c r="B23" t="str">
         <v>ATG</v>
@@ -1999,28 +2179,28 @@
         <v>UP</v>
       </c>
       <c r="G23" t="str">
-        <v>95/47</v>
+        <v>97/3</v>
       </c>
       <c r="H23" t="str">
         <v>Manual</v>
       </c>
       <c r="I23" t="str">
-        <v>Home</v>
+        <v>Distant</v>
       </c>
       <c r="J23" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="K23" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -2029,39 +2209,39 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <v>0</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="V23">
         <v>1</v>
       </c>
       <c r="W23" t="str">
-        <v>RI:L1=UP LL</v>
+        <v/>
       </c>
       <c r="X23" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
+        <v/>
       </c>
       <c r="Y23">
-        <v>95.62299999999999</v>
+        <v>96.36</v>
       </c>
       <c r="Z23" t="str">
-        <v>95/47</v>
+        <v>97/3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ATG S-18</v>
+        <v>ATG S-27</v>
       </c>
       <c r="B24" t="str">
         <v>ATG</v>
@@ -2079,25 +2259,25 @@
         <v>UP</v>
       </c>
       <c r="G24" t="str">
-        <v>PF-2 STR</v>
+        <v>95/47</v>
       </c>
       <c r="H24" t="str">
         <v>Manual</v>
       </c>
       <c r="I24" t="str">
-        <v>Starter</v>
+        <v>Home</v>
       </c>
       <c r="J24" t="str">
-        <v>Right</v>
+        <v>Extreme Right</v>
       </c>
       <c r="K24" t="str">
         <v>Left</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -2109,30 +2289,39 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
         <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="V24">
         <v>1</v>
       </c>
+      <c r="W24" t="str">
+        <v>RI:L1=UP LL</v>
+      </c>
+      <c r="X24" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
       <c r="Y24">
-        <v>95.219</v>
+        <v>95.62299999999999</v>
+      </c>
+      <c r="Z24" t="str">
+        <v>95/47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ATG S-17</v>
+        <v>ATG S-18</v>
       </c>
       <c r="B25" t="str">
         <v>ATG</v>
@@ -2150,28 +2339,28 @@
         <v>UP</v>
       </c>
       <c r="G25" t="str">
-        <v>94/27</v>
+        <v>PF-2 STR</v>
       </c>
       <c r="H25" t="str">
         <v>Manual</v>
       </c>
       <c r="I25" t="str">
-        <v>Advanced Starter</v>
+        <v>Starter</v>
       </c>
       <c r="J25" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="K25" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2192,21 +2381,33 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="V25">
         <v>1</v>
       </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
       <c r="Y25">
-        <v>94.089</v>
+        <v>95.219</v>
       </c>
       <c r="Z25" t="str">
-        <v>94/27</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Gate-69</v>
+        <v>ATG S-19</v>
+      </c>
+      <c r="B26" t="str">
+        <v>ATG</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Atgaon</v>
       </c>
       <c r="D26" t="str">
         <v>KYN-KSRA</v>
@@ -2218,16 +2419,19 @@
         <v>UP</v>
       </c>
       <c r="G26" t="str">
-        <v>93/11</v>
+        <v>UP LOOP STR</v>
       </c>
       <c r="H26" t="str">
-        <v>Gate</v>
+        <v>Manual</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Starter (Loop)</v>
       </c>
       <c r="J26" t="str">
         <v>Left</v>
       </c>
       <c r="K26" t="str">
-        <v>Right</v>
+        <v/>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2256,22 +2460,34 @@
       <c r="T26">
         <v>0</v>
       </c>
-      <c r="U26">
-        <v>300</v>
+      <c r="U26" t="str">
+        <v/>
       </c>
       <c r="V26">
         <v>1</v>
       </c>
-      <c r="Y26">
-        <v>92.60900000000001</v>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
       </c>
       <c r="Z26" t="str">
-        <v>93/11</v>
+        <v>94/41A</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ATG IBS DIST</v>
+        <v>ATG S-17</v>
+      </c>
+      <c r="B27" t="str">
+        <v>ATG</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Atgaon</v>
       </c>
       <c r="D27" t="str">
         <v>KYN-KSRA</v>
@@ -2283,19 +2499,19 @@
         <v>UP</v>
       </c>
       <c r="G27" t="str">
-        <v>90/41</v>
+        <v>94/27</v>
       </c>
       <c r="H27" t="str">
         <v>Manual</v>
       </c>
       <c r="I27" t="str">
-        <v>IBS Distant</v>
+        <v>Advanced Starter</v>
       </c>
       <c r="J27" t="str">
         <v>Left</v>
       </c>
       <c r="K27" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2325,21 +2541,33 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="V27">
         <v>1</v>
       </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
       <c r="Y27">
-        <v>91.613</v>
+        <v>94.089</v>
       </c>
       <c r="Z27" t="str">
-        <v>90/41</v>
+        <v>94/27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ATG S-16</v>
+        <v>Gate-69</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
       </c>
       <c r="D28" t="str">
         <v>KYN-KSRA</v>
@@ -2351,19 +2579,19 @@
         <v>UP</v>
       </c>
       <c r="G28" t="str">
-        <v>89/33</v>
+        <v>93/11</v>
       </c>
       <c r="H28" t="str">
-        <v>IBS</v>
+        <v>Gate</v>
       </c>
       <c r="I28" t="str">
-        <v>IBS</v>
+        <v/>
       </c>
       <c r="J28" t="str">
         <v>Left</v>
       </c>
       <c r="K28" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2398,22 +2626,28 @@
       <c r="V28">
         <v>1</v>
       </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
       <c r="Y28">
-        <v>90.033</v>
+        <v>92.60900000000001</v>
       </c>
       <c r="Z28" t="str">
-        <v>89/33</v>
+        <v>93/11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ASO DIST</v>
+        <v>ATG IBS DIST</v>
       </c>
       <c r="B29" t="str">
-        <v>ASO</v>
+        <v/>
       </c>
       <c r="C29" t="str">
-        <v>Asangaon</v>
+        <v/>
       </c>
       <c r="D29" t="str">
         <v>KYN-KSRA</v>
@@ -2425,16 +2659,19 @@
         <v>UP</v>
       </c>
       <c r="G29" t="str">
-        <v>87/7</v>
+        <v>90/41</v>
       </c>
       <c r="H29" t="str">
         <v>Manual</v>
       </c>
+      <c r="I29" t="str">
+        <v>IBS Distant</v>
+      </c>
       <c r="J29" t="str">
         <v>Left</v>
       </c>
       <c r="K29" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2469,22 +2706,28 @@
       <c r="V29">
         <v>1</v>
       </c>
+      <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
       <c r="Y29">
-        <v>88.833</v>
+        <v>91.613</v>
       </c>
       <c r="Z29" t="str">
-        <v>87/7</v>
+        <v>90/41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ASO S-28</v>
+        <v>ATG S-16</v>
       </c>
       <c r="B30" t="str">
-        <v>ASO</v>
+        <v/>
       </c>
       <c r="C30" t="str">
-        <v>Asangaon</v>
+        <v/>
       </c>
       <c r="D30" t="str">
         <v>KYN-KSRA</v>
@@ -2496,16 +2739,19 @@
         <v>UP</v>
       </c>
       <c r="G30" t="str">
-        <v>86/11</v>
+        <v>89/33</v>
       </c>
       <c r="H30" t="str">
-        <v>Manual</v>
+        <v>IBS</v>
+      </c>
+      <c r="I30" t="str">
+        <v>IBS</v>
       </c>
       <c r="J30" t="str">
         <v>Left</v>
       </c>
       <c r="K30" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2523,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30">
         <v>0</v>
       </c>
       <c r="S30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -2541,21 +2787,21 @@
         <v>1</v>
       </c>
       <c r="W30" t="str">
-        <v>RI:L1=UP LL</v>
+        <v/>
       </c>
       <c r="X30" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
+        <v/>
       </c>
       <c r="Y30">
-        <v>85.87299999999999</v>
+        <v>90.033</v>
       </c>
       <c r="Z30" t="str">
-        <v>86/11</v>
+        <v>89/33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ASO S-23</v>
+        <v>ASO DIST</v>
       </c>
       <c r="B31" t="str">
         <v>ASO</v>
@@ -2573,16 +2819,19 @@
         <v>UP</v>
       </c>
       <c r="G31" t="str">
-        <v>PF-2 STR</v>
+        <v>87/7</v>
       </c>
       <c r="H31" t="str">
         <v>Manual</v>
       </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
       <c r="J31" t="str">
         <v>Left</v>
       </c>
       <c r="K31" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2612,18 +2861,27 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="V31">
         <v>1</v>
       </c>
+      <c r="W31" t="str">
+        <v/>
+      </c>
+      <c r="X31" t="str">
+        <v/>
+      </c>
       <c r="Y31">
-        <v>85.479</v>
+        <v>88.833</v>
+      </c>
+      <c r="Z31" t="str">
+        <v>87/7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ASO S-22</v>
+        <v>ASO S-28</v>
       </c>
       <c r="B32" t="str">
         <v>ASO</v>
@@ -2641,25 +2899,28 @@
         <v>UP</v>
       </c>
       <c r="G32" t="str">
-        <v>PF-1 STR</v>
+        <v>86/11</v>
       </c>
       <c r="H32" t="str">
         <v>Manual</v>
       </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
       <c r="J32" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="K32" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2668,30 +2929,39 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32">
         <v>0</v>
       </c>
       <c r="U32">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="V32">
         <v>1</v>
       </c>
+      <c r="W32" t="str">
+        <v>RI:L1=UP LL</v>
+      </c>
+      <c r="X32" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
       <c r="Y32">
-        <v>84.299</v>
+        <v>85.87299999999999</v>
+      </c>
+      <c r="Z32" t="str">
+        <v>86/11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ASO S-18</v>
+        <v>ASO S-23</v>
       </c>
       <c r="B33" t="str">
         <v>ASO</v>
@@ -2709,25 +2979,28 @@
         <v>UP</v>
       </c>
       <c r="G33" t="str">
-        <v>84/25</v>
+        <v>PF-2 STR</v>
       </c>
       <c r="H33" t="str">
         <v>Manual</v>
       </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
       <c r="J33" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="K33" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2753,16 +3026,28 @@
       <c r="V33">
         <v>1</v>
       </c>
+      <c r="W33" t="str">
+        <v/>
+      </c>
+      <c r="X33" t="str">
+        <v/>
+      </c>
       <c r="Y33">
-        <v>83.279</v>
+        <v>85.479</v>
       </c>
       <c r="Z33" t="str">
-        <v>84/25</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ASO IBS DIST</v>
+        <v>ASO S-22</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ASO</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Asangaon</v>
       </c>
       <c r="D34" t="str">
         <v>KYN-KSRA</v>
@@ -2774,28 +3059,28 @@
         <v>UP</v>
       </c>
       <c r="G34" t="str">
-        <v>83/29</v>
+        <v>PF-1 STR</v>
       </c>
       <c r="H34" t="str">
         <v>Manual</v>
       </c>
       <c r="I34" t="str">
-        <v>IBS Distant</v>
+        <v/>
       </c>
       <c r="J34" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="K34" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2816,21 +3101,33 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="V34">
         <v>1</v>
       </c>
+      <c r="W34" t="str">
+        <v/>
+      </c>
+      <c r="X34" t="str">
+        <v/>
+      </c>
       <c r="Y34">
-        <v>81.819</v>
+        <v>84.299</v>
       </c>
       <c r="Z34" t="str">
-        <v>83/29</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ASO S-16</v>
+        <v>ASO S-24</v>
+      </c>
+      <c r="B35" t="str">
+        <v>ASO</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Asangaon</v>
       </c>
       <c r="D35" t="str">
         <v>KYN-KSRA</v>
@@ -2842,19 +3139,19 @@
         <v>UP</v>
       </c>
       <c r="G35" t="str">
-        <v>82/33</v>
+        <v>UP LOOP STR</v>
       </c>
       <c r="H35" t="str">
-        <v>IBS</v>
+        <v>Manual</v>
       </c>
       <c r="I35" t="str">
-        <v>IBS</v>
+        <v>Starter (Loop)</v>
       </c>
       <c r="J35" t="str">
         <v>Left</v>
       </c>
       <c r="K35" t="str">
-        <v>Right</v>
+        <v/>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2883,22 +3180,34 @@
       <c r="T35">
         <v>0</v>
       </c>
-      <c r="U35">
-        <v>600</v>
+      <c r="U35" t="str">
+        <v/>
       </c>
       <c r="V35">
         <v>1</v>
       </c>
-      <c r="Y35">
-        <v>80.309</v>
+      <c r="W35" t="str">
+        <v/>
+      </c>
+      <c r="X35" t="str">
+        <v/>
+      </c>
+      <c r="Y35" t="str">
+        <v/>
       </c>
       <c r="Z35" t="str">
-        <v>82/33</v>
+        <v>84/51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gate-64</v>
+        <v>ASO S-18</v>
+      </c>
+      <c r="B36" t="str">
+        <v>ASO</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Asangaon</v>
       </c>
       <c r="D36" t="str">
         <v>KYN-KSRA</v>
@@ -2910,25 +3219,28 @@
         <v>UP</v>
       </c>
       <c r="G36" t="str">
-        <v>81/3</v>
+        <v>84/25</v>
       </c>
       <c r="H36" t="str">
-        <v>Gate</v>
+        <v>Manual</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
       </c>
       <c r="J36" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="K36" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2949,27 +3261,33 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="V36">
         <v>1</v>
       </c>
+      <c r="W36" t="str">
+        <v/>
+      </c>
+      <c r="X36" t="str">
+        <v/>
+      </c>
       <c r="Y36">
-        <v>79.856</v>
+        <v>83.279</v>
       </c>
       <c r="Z36" t="str">
-        <v>81/3</v>
+        <v>84/25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>VSD S-42</v>
+        <v>ASO IBS DIST</v>
       </c>
       <c r="B37" t="str">
-        <v>VSD</v>
+        <v/>
       </c>
       <c r="C37" t="str">
-        <v>Vasind</v>
+        <v/>
       </c>
       <c r="D37" t="str">
         <v>KYN-KSRA</v>
@@ -2981,16 +3299,19 @@
         <v>UP</v>
       </c>
       <c r="G37" t="str">
-        <v>80/3</v>
+        <v>83/29</v>
       </c>
       <c r="H37" t="str">
         <v>Manual</v>
       </c>
+      <c r="I37" t="str">
+        <v>IBS Distant</v>
+      </c>
       <c r="J37" t="str">
         <v>Left</v>
       </c>
       <c r="K37" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3008,45 +3329,45 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <v>0</v>
       </c>
       <c r="S37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="V37">
         <v>1</v>
       </c>
       <c r="W37" t="str">
-        <v>RI:L1=UP LL; R1=UDL</v>
+        <v/>
       </c>
       <c r="X37" t="str">
-        <v>Book shows one left and one right arm on top of vertical stem</v>
+        <v/>
       </c>
       <c r="Y37">
-        <v>79.459</v>
+        <v>81.819</v>
       </c>
       <c r="Z37" t="str">
-        <v>80/3</v>
+        <v>83/29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>VSD S-39</v>
+        <v>ASO S-16</v>
       </c>
       <c r="B38" t="str">
-        <v>VSD</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>Vasind</v>
+        <v/>
       </c>
       <c r="D38" t="str">
         <v>KYN-KSRA</v>
@@ -3058,16 +3379,19 @@
         <v>UP</v>
       </c>
       <c r="G38" t="str">
-        <v>PF-2 STR</v>
+        <v>82/33</v>
       </c>
       <c r="H38" t="str">
-        <v>Manual</v>
+        <v>IBS</v>
+      </c>
+      <c r="I38" t="str">
+        <v>IBS</v>
       </c>
       <c r="J38" t="str">
         <v>Left</v>
       </c>
       <c r="K38" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3088,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -3097,21 +3421,33 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V38">
         <v>1</v>
+      </c>
+      <c r="W38" t="str">
+        <v/>
+      </c>
+      <c r="X38" t="str">
+        <v/>
+      </c>
+      <c r="Y38">
+        <v>80.309</v>
+      </c>
+      <c r="Z38" t="str">
+        <v>82/33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>VSD S-22</v>
+        <v>Gate-64</v>
       </c>
       <c r="B39" t="str">
-        <v>VSD</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>Vasind</v>
+        <v/>
       </c>
       <c r="D39" t="str">
         <v>KYN-KSRA</v>
@@ -3123,10 +3459,13 @@
         <v>UP</v>
       </c>
       <c r="G39" t="str">
-        <v>78/23</v>
+        <v>81/3</v>
       </c>
       <c r="H39" t="str">
-        <v>Manual</v>
+        <v>Gate</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
       </c>
       <c r="J39" t="str">
         <v>Left</v>
@@ -3162,21 +3501,33 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="V39">
         <v>1</v>
       </c>
+      <c r="W39" t="str">
+        <v/>
+      </c>
+      <c r="X39" t="str">
+        <v/>
+      </c>
       <c r="Y39">
-        <v>78.249</v>
+        <v>79.856</v>
       </c>
       <c r="Z39" t="str">
-        <v>78/23</v>
+        <v>81/3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>VSD IBS DIST</v>
+        <v>VSD S-42</v>
+      </c>
+      <c r="B40" t="str">
+        <v>VSD</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Vasind</v>
       </c>
       <c r="D40" t="str">
         <v>KYN-KSRA</v>
@@ -3188,13 +3539,13 @@
         <v>UP</v>
       </c>
       <c r="G40" t="str">
-        <v>76/25</v>
+        <v>80/3</v>
       </c>
       <c r="H40" t="str">
         <v>Manual</v>
       </c>
       <c r="I40" t="str">
-        <v>IBS Distant</v>
+        <v/>
       </c>
       <c r="J40" t="str">
         <v>Left</v>
@@ -3218,33 +3569,45 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40">
         <v>0</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="V40">
         <v>1</v>
       </c>
+      <c r="W40" t="str">
+        <v>RI:L1=UP LL; R1=UDL</v>
+      </c>
+      <c r="X40" t="str">
+        <v>Book shows one left and one right arm on top of vertical stem</v>
+      </c>
       <c r="Y40">
-        <v>76.899</v>
+        <v>79.459</v>
       </c>
       <c r="Z40" t="str">
-        <v>76/25</v>
+        <v>80/3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>VSD S-23</v>
+        <v>VSD S-39</v>
+      </c>
+      <c r="B41" t="str">
+        <v>VSD</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Vasind</v>
       </c>
       <c r="D41" t="str">
         <v>KYN-KSRA</v>
@@ -3256,13 +3619,13 @@
         <v>UP</v>
       </c>
       <c r="G41" t="str">
-        <v>75/19</v>
+        <v>PF-2 STR</v>
       </c>
       <c r="H41" t="str">
-        <v>IBS</v>
+        <v>Manual</v>
       </c>
       <c r="I41" t="str">
-        <v>IBS</v>
+        <v/>
       </c>
       <c r="J41" t="str">
         <v>Left</v>
@@ -3289,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -3298,27 +3661,33 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="V41">
         <v>1</v>
       </c>
-      <c r="Y41">
-        <v>75.499</v>
+      <c r="W41" t="str">
+        <v/>
+      </c>
+      <c r="X41" t="str">
+        <v/>
+      </c>
+      <c r="Y41" t="str">
+        <v/>
       </c>
       <c r="Z41" t="str">
-        <v>75/19</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>KDV DIST</v>
+        <v>VSD S-36</v>
       </c>
       <c r="B42" t="str">
-        <v>KDV</v>
+        <v>VSD</v>
       </c>
       <c r="C42" t="str">
-        <v>Khadavli</v>
+        <v>Vasind</v>
       </c>
       <c r="D42" t="str">
         <v>KYN-KSRA</v>
@@ -3330,11 +3699,14 @@
         <v>UP</v>
       </c>
       <c r="G42" t="str">
-        <v>73/27</v>
+        <v>UP LOOP STR</v>
       </c>
       <c r="H42" t="str">
         <v>Manual</v>
       </c>
+      <c r="I42" t="str">
+        <v>Starter (Loop)</v>
+      </c>
       <c r="J42" t="str">
         <v>Left</v>
       </c>
@@ -3360,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -3369,27 +3741,33 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="V42">
         <v>1</v>
       </c>
-      <c r="Y42">
-        <v>74.459</v>
+      <c r="W42" t="str">
+        <v/>
+      </c>
+      <c r="X42" t="str">
+        <v/>
+      </c>
+      <c r="Y42" t="str">
+        <v/>
       </c>
       <c r="Z42" t="str">
-        <v>73/27</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>KDV S-27</v>
+        <v>VSD S-37</v>
       </c>
       <c r="B43" t="str">
-        <v>KDV</v>
+        <v>VSD</v>
       </c>
       <c r="C43" t="str">
-        <v>Khadavli</v>
+        <v>Vasind</v>
       </c>
       <c r="D43" t="str">
         <v>KYN-KSRA</v>
@@ -3401,16 +3779,19 @@
         <v>UP</v>
       </c>
       <c r="G43" t="str">
-        <v>72/37</v>
+        <v>UDL UP STR</v>
       </c>
       <c r="H43" t="str">
         <v>Manual</v>
       </c>
+      <c r="I43" t="str">
+        <v>Starter (Loop)</v>
+      </c>
       <c r="J43" t="str">
         <v>Left</v>
       </c>
       <c r="K43" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -3428,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43">
         <v>0</v>
@@ -3446,27 +3827,27 @@
         <v>1</v>
       </c>
       <c r="W43" t="str">
-        <v>RI:L1=UP LL</v>
+        <v/>
       </c>
       <c r="X43" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
-      </c>
-      <c r="Y43">
-        <v>72.589</v>
+        <v/>
+      </c>
+      <c r="Y43" t="str">
+        <v/>
       </c>
       <c r="Z43" t="str">
-        <v>72/37</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>KDV S-18</v>
+        <v>VSD S-22</v>
       </c>
       <c r="B44" t="str">
-        <v>KDV</v>
+        <v>VSD</v>
       </c>
       <c r="C44" t="str">
-        <v>Khadavli</v>
+        <v>Vasind</v>
       </c>
       <c r="D44" t="str">
         <v>KYN-KSRA</v>
@@ -3478,13 +3859,16 @@
         <v>UP</v>
       </c>
       <c r="G44" t="str">
-        <v>PF-2 STR</v>
+        <v>78/23</v>
       </c>
       <c r="H44" t="str">
         <v>Manual</v>
       </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
       <c r="J44" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="K44" t="str">
         <v>Unknown</v>
@@ -3493,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3517,24 +3901,33 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V44">
         <v>1</v>
       </c>
+      <c r="W44" t="str">
+        <v/>
+      </c>
+      <c r="X44" t="str">
+        <v/>
+      </c>
       <c r="Y44">
-        <v>72.129</v>
+        <v>78.249</v>
+      </c>
+      <c r="Z44" t="str">
+        <v>78/23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>KDV S-17</v>
+        <v>VSD IBS DIST</v>
       </c>
       <c r="B45" t="str">
-        <v>KDV</v>
+        <v/>
       </c>
       <c r="C45" t="str">
-        <v>Khadavli</v>
+        <v/>
       </c>
       <c r="D45" t="str">
         <v>KYN-KSRA</v>
@@ -3546,16 +3939,19 @@
         <v>UP</v>
       </c>
       <c r="G45" t="str">
-        <v>71/7</v>
+        <v>76/25</v>
       </c>
       <c r="H45" t="str">
         <v>Manual</v>
       </c>
+      <c r="I45" t="str">
+        <v>IBS Distant</v>
+      </c>
       <c r="J45" t="str">
         <v>Left</v>
       </c>
       <c r="K45" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -3585,21 +3981,33 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="V45">
         <v>1</v>
       </c>
+      <c r="W45" t="str">
+        <v/>
+      </c>
+      <c r="X45" t="str">
+        <v/>
+      </c>
       <c r="Y45">
-        <v>70.799</v>
+        <v>76.899</v>
       </c>
       <c r="Z45" t="str">
-        <v>71/7</v>
+        <v>76/25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Gate-55</v>
+        <v>VSD S-23</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
       </c>
       <c r="D46" t="str">
         <v>KYN-KSRA</v>
@@ -3611,10 +4019,13 @@
         <v>UP</v>
       </c>
       <c r="G46" t="str">
-        <v>69/35</v>
+        <v>75/19</v>
       </c>
       <c r="H46" t="str">
-        <v>Gate</v>
+        <v>IBS</v>
+      </c>
+      <c r="I46" t="str">
+        <v>IBS</v>
       </c>
       <c r="J46" t="str">
         <v>Left</v>
@@ -3650,21 +4061,33 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V46">
         <v>1</v>
       </c>
+      <c r="W46" t="str">
+        <v/>
+      </c>
+      <c r="X46" t="str">
+        <v/>
+      </c>
       <c r="Y46">
-        <v>69.439</v>
+        <v>75.499</v>
       </c>
       <c r="Z46" t="str">
-        <v>69/35</v>
+        <v>75/19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Gate-54</v>
+        <v>KDV DIST</v>
+      </c>
+      <c r="B47" t="str">
+        <v>KDV</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Khadavli</v>
       </c>
       <c r="D47" t="str">
         <v>KYN-KSRA</v>
@@ -3676,10 +4099,13 @@
         <v>UP</v>
       </c>
       <c r="G47" t="str">
-        <v>68/29</v>
+        <v>73/27</v>
       </c>
       <c r="H47" t="str">
-        <v>Gate</v>
+        <v>Manual</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
       </c>
       <c r="J47" t="str">
         <v>Left</v>
@@ -3720,16 +4146,28 @@
       <c r="V47">
         <v>1</v>
       </c>
+      <c r="W47" t="str">
+        <v/>
+      </c>
+      <c r="X47" t="str">
+        <v/>
+      </c>
       <c r="Y47">
-        <v>67.889</v>
+        <v>74.459</v>
       </c>
       <c r="Z47" t="str">
-        <v>68/29</v>
+        <v>73/27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>KDV S-16</v>
+        <v>KDV S-27</v>
+      </c>
+      <c r="B48" t="str">
+        <v>KDV</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Khadavli</v>
       </c>
       <c r="D48" t="str">
         <v>KYN-KSRA</v>
@@ -3741,19 +4179,19 @@
         <v>UP</v>
       </c>
       <c r="G48" t="str">
-        <v>67/41</v>
+        <v>72/37</v>
       </c>
       <c r="H48" t="str">
-        <v>IBS</v>
+        <v>Manual</v>
       </c>
       <c r="I48" t="str">
-        <v>IBS</v>
+        <v/>
       </c>
       <c r="J48" t="str">
         <v>Left</v>
       </c>
       <c r="K48" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -3771,33 +4209,45 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>0</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48">
         <v>0</v>
       </c>
       <c r="U48">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="V48">
         <v>1</v>
       </c>
+      <c r="W48" t="str">
+        <v>RI:L1=UP LL</v>
+      </c>
+      <c r="X48" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
       <c r="Y48">
-        <v>66.739</v>
+        <v>72.589</v>
       </c>
       <c r="Z48" t="str">
-        <v>67/41</v>
+        <v>72/37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Gate-52</v>
+        <v>KDV S-18</v>
+      </c>
+      <c r="B49" t="str">
+        <v>KDV</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Khadavli</v>
       </c>
       <c r="D49" t="str">
         <v>KYN-KSRA</v>
@@ -3809,25 +4259,28 @@
         <v>UP</v>
       </c>
       <c r="G49" t="str">
-        <v>66/35</v>
+        <v>PF-2 STR</v>
       </c>
       <c r="H49" t="str">
-        <v>Gate</v>
+        <v>Manual</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
       </c>
       <c r="J49" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="K49" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -3848,27 +4301,33 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="V49">
         <v>1</v>
       </c>
+      <c r="W49" t="str">
+        <v/>
+      </c>
+      <c r="X49" t="str">
+        <v/>
+      </c>
       <c r="Y49">
-        <v>66.055</v>
+        <v>72.129</v>
       </c>
       <c r="Z49" t="str">
-        <v>66/35</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TLA DIST</v>
+        <v>KDV S-19</v>
       </c>
       <c r="B50" t="str">
-        <v>TLA</v>
+        <v>KDV</v>
       </c>
       <c r="C50" t="str">
-        <v>Titwala</v>
+        <v>Khadavli</v>
       </c>
       <c r="D50" t="str">
         <v>KYN-KSRA</v>
@@ -3880,16 +4339,19 @@
         <v>UP</v>
       </c>
       <c r="G50" t="str">
-        <v>65/41</v>
+        <v>UP LOOP STR</v>
       </c>
       <c r="H50" t="str">
         <v>Manual</v>
       </c>
+      <c r="I50" t="str">
+        <v>Starter (Loop)</v>
+      </c>
       <c r="J50" t="str">
         <v>Left</v>
       </c>
       <c r="K50" t="str">
-        <v>Right</v>
+        <v/>
       </c>
       <c r="L50">
         <v>0</v>
@@ -3918,28 +4380,34 @@
       <c r="T50">
         <v>0</v>
       </c>
-      <c r="U50">
-        <v>425</v>
+      <c r="U50" t="str">
+        <v/>
       </c>
       <c r="V50">
         <v>1</v>
       </c>
-      <c r="Y50">
-        <v>65.045</v>
+      <c r="W50" t="str">
+        <v/>
+      </c>
+      <c r="X50" t="str">
+        <v/>
+      </c>
+      <c r="Y50" t="str">
+        <v/>
       </c>
       <c r="Z50" t="str">
-        <v>65/41</v>
+        <v>71/28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TLA S-25</v>
+        <v>KDV S-17</v>
       </c>
       <c r="B51" t="str">
-        <v>TLA</v>
+        <v>KDV</v>
       </c>
       <c r="C51" t="str">
-        <v>Titwala</v>
+        <v>Khadavli</v>
       </c>
       <c r="D51" t="str">
         <v>KYN-KSRA</v>
@@ -3951,11 +4419,14 @@
         <v>UP</v>
       </c>
       <c r="G51" t="str">
-        <v>64/41</v>
+        <v>71/7</v>
       </c>
       <c r="H51" t="str">
         <v>Manual</v>
       </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
       <c r="J51" t="str">
         <v>Left</v>
       </c>
@@ -3978,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -3990,27 +4461,33 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="V51">
         <v>1</v>
       </c>
+      <c r="W51" t="str">
+        <v/>
+      </c>
+      <c r="X51" t="str">
+        <v/>
+      </c>
       <c r="Y51">
-        <v>64.494</v>
+        <v>70.799</v>
       </c>
       <c r="Z51" t="str">
-        <v>64/41</v>
+        <v>71/7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>TLA S-21</v>
+        <v>Gate-55</v>
       </c>
       <c r="B52" t="str">
-        <v>TLA</v>
+        <v/>
       </c>
       <c r="C52" t="str">
-        <v>Titwala</v>
+        <v/>
       </c>
       <c r="D52" t="str">
         <v>KYN-KSRA</v>
@@ -4022,10 +4499,13 @@
         <v>UP</v>
       </c>
       <c r="G52" t="str">
-        <v>PF-3 STR</v>
+        <v>69/35</v>
       </c>
       <c r="H52" t="str">
-        <v>Manual</v>
+        <v>Gate</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
       </c>
       <c r="J52" t="str">
         <v>Left</v>
@@ -4049,39 +4529,45 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52">
         <v>0</v>
       </c>
       <c r="U52">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="V52">
         <v>1</v>
       </c>
       <c r="W52" t="str">
-        <v>RI:L1=UP LL</v>
+        <v/>
       </c>
       <c r="X52" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
+        <v/>
+      </c>
+      <c r="Y52">
+        <v>69.439</v>
+      </c>
+      <c r="Z52" t="str">
+        <v>69/35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>TLA S-22</v>
+        <v>Gate-54</v>
       </c>
       <c r="B53" t="str">
-        <v>TLA</v>
+        <v/>
       </c>
       <c r="C53" t="str">
-        <v>Titwala</v>
+        <v/>
       </c>
       <c r="D53" t="str">
         <v>KYN-KSRA</v>
@@ -4093,25 +4579,28 @@
         <v>UP</v>
       </c>
       <c r="G53" t="str">
-        <v>PF-2 STR</v>
+        <v>68/29</v>
       </c>
       <c r="H53" t="str">
-        <v>Manual</v>
+        <v>Gate</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="K53" t="str">
         <v>Unknown</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -4120,42 +4609,45 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53">
         <v>0</v>
       </c>
       <c r="U53">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="V53">
         <v>1</v>
       </c>
       <c r="W53" t="str">
-        <v>RI:L1=UP LL</v>
+        <v/>
       </c>
       <c r="X53" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
+        <v/>
       </c>
       <c r="Y53">
-        <v>64.113</v>
+        <v>67.889</v>
+      </c>
+      <c r="Z53" t="str">
+        <v>68/29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>TLA S-19</v>
+        <v>KDV S-16</v>
       </c>
       <c r="B54" t="str">
-        <v>TLA</v>
+        <v/>
       </c>
       <c r="C54" t="str">
-        <v>Titwala</v>
+        <v/>
       </c>
       <c r="D54" t="str">
         <v>KYN-KSRA</v>
@@ -4167,25 +4659,28 @@
         <v>UP</v>
       </c>
       <c r="G54" t="str">
-        <v>63/03</v>
+        <v>67/41</v>
       </c>
       <c r="H54" t="str">
-        <v>Manual</v>
+        <v>IBS</v>
+      </c>
+      <c r="I54" t="str">
+        <v>IBS</v>
       </c>
       <c r="J54" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="K54" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -4206,21 +4701,33 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V54">
         <v>1</v>
       </c>
+      <c r="W54" t="str">
+        <v/>
+      </c>
+      <c r="X54" t="str">
+        <v/>
+      </c>
       <c r="Y54">
-        <v>63.686</v>
+        <v>66.739</v>
       </c>
       <c r="Z54" t="str">
-        <v>63/03</v>
+        <v>67/41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>NE-6212</v>
+        <v>Gate-52</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
       </c>
       <c r="D55" t="str">
         <v>KYN-KSRA</v>
@@ -4232,10 +4739,13 @@
         <v>UP</v>
       </c>
       <c r="G55" t="str">
-        <v>62/29</v>
+        <v>66/35</v>
       </c>
       <c r="H55" t="str">
-        <v>Automatic</v>
+        <v>Gate</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
       </c>
       <c r="J55" t="str">
         <v>Left</v>
@@ -4271,21 +4781,33 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="V55">
         <v>1</v>
       </c>
+      <c r="W55" t="str">
+        <v/>
+      </c>
+      <c r="X55" t="str">
+        <v/>
+      </c>
       <c r="Y55">
-        <v>62.356</v>
+        <v>66.055</v>
       </c>
       <c r="Z55" t="str">
-        <v>62/29</v>
+        <v>66/35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>NE-6114</v>
+        <v>TLA DIST</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TLA</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Titwala</v>
       </c>
       <c r="D56" t="str">
         <v>KYN-KSRA</v>
@@ -4297,16 +4819,19 @@
         <v>UP</v>
       </c>
       <c r="G56" t="str">
-        <v>61/31</v>
+        <v>65/41</v>
       </c>
       <c r="H56" t="str">
-        <v>Automatic</v>
+        <v>Manual</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
       </c>
       <c r="J56" t="str">
         <v>Left</v>
       </c>
       <c r="K56" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4336,21 +4861,33 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="V56">
         <v>1</v>
       </c>
+      <c r="W56" t="str">
+        <v/>
+      </c>
+      <c r="X56" t="str">
+        <v/>
+      </c>
       <c r="Y56">
-        <v>61.636</v>
+        <v>65.045</v>
       </c>
       <c r="Z56" t="str">
-        <v>61/31</v>
+        <v>65/41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>NE-6102</v>
+        <v>TLA S-25</v>
+      </c>
+      <c r="B57" t="str">
+        <v>TLA</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Titwala</v>
       </c>
       <c r="D57" t="str">
         <v>KYN-KSRA</v>
@@ -4362,16 +4899,19 @@
         <v>UP</v>
       </c>
       <c r="G57" t="str">
-        <v>61/05</v>
+        <v>64/41</v>
       </c>
       <c r="H57" t="str">
-        <v>Automatic</v>
+        <v>Manual</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
       </c>
       <c r="J57" t="str">
         <v>Left</v>
       </c>
       <c r="K57" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4389,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -4401,21 +4941,33 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V57">
         <v>1</v>
       </c>
+      <c r="W57" t="str">
+        <v/>
+      </c>
+      <c r="X57" t="str">
+        <v/>
+      </c>
       <c r="Y57">
-        <v>60.908</v>
+        <v>64.494</v>
       </c>
       <c r="Z57" t="str">
-        <v>61/05</v>
+        <v>64/41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>NE-6008</v>
+        <v>TLA S-21</v>
+      </c>
+      <c r="B58" t="str">
+        <v>TLA</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Titwala</v>
       </c>
       <c r="D58" t="str">
         <v>KYN-KSRA</v>
@@ -4427,16 +4979,19 @@
         <v>UP</v>
       </c>
       <c r="G58" t="str">
-        <v>60/15</v>
+        <v>PF-3 STR</v>
       </c>
       <c r="H58" t="str">
-        <v>Automatic</v>
+        <v>Manual</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
       </c>
       <c r="J58" t="str">
         <v>Left</v>
       </c>
       <c r="K58" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -4454,33 +5009,45 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58">
         <v>0</v>
       </c>
       <c r="U58">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="V58">
         <v>1</v>
       </c>
-      <c r="Y58">
-        <v>60.132</v>
+      <c r="W58" t="str">
+        <v>RI:L1=UP LL</v>
+      </c>
+      <c r="X58" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
+      <c r="Y58" t="str">
+        <v/>
       </c>
       <c r="Z58" t="str">
-        <v>60/15</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Gate-48</v>
+        <v>TLA S-22</v>
+      </c>
+      <c r="B59" t="str">
+        <v>TLA</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Titwala</v>
       </c>
       <c r="D59" t="str">
         <v>KYN-KSRA</v>
@@ -4492,25 +5059,28 @@
         <v>UP</v>
       </c>
       <c r="G59" t="str">
-        <v>59/39</v>
+        <v>PF-2 STR</v>
       </c>
       <c r="H59" t="str">
-        <v>Automatic</v>
+        <v>Manual</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
       </c>
       <c r="J59" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="K59" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -4519,13 +5089,13 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59">
         <v>0</v>
@@ -4536,16 +5106,28 @@
       <c r="V59">
         <v>1</v>
       </c>
+      <c r="W59" t="str">
+        <v>RI:L1=UP LL</v>
+      </c>
+      <c r="X59" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
       <c r="Y59">
-        <v>59.375</v>
+        <v>64.113</v>
       </c>
       <c r="Z59" t="str">
-        <v>59/39</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>NE-5918</v>
+        <v>TLA S-20</v>
+      </c>
+      <c r="B60" t="str">
+        <v>TLA</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Titwala</v>
       </c>
       <c r="D60" t="str">
         <v>KYN-KSRA</v>
@@ -4557,25 +5139,28 @@
         <v>UP</v>
       </c>
       <c r="G60" t="str">
-        <v>59/07</v>
+        <v>UP LOOP STR</v>
       </c>
       <c r="H60" t="str">
-        <v>Automatic</v>
+        <v>Manual</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Starter (Loop)</v>
       </c>
       <c r="J60" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="K60" t="str">
-        <v>Left</v>
+        <v/>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -4593,24 +5178,36 @@
         <v>0</v>
       </c>
       <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>210</v>
+        <v>1</v>
+      </c>
+      <c r="U60" t="str">
+        <v/>
       </c>
       <c r="V60">
         <v>1</v>
       </c>
-      <c r="Y60">
-        <v>58.801</v>
+      <c r="W60" t="str">
+        <v>RI:L1=UP LL</v>
+      </c>
+      <c r="X60" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
+      <c r="Y60" t="str">
+        <v/>
       </c>
       <c r="Z60" t="str">
-        <v>59/07</v>
+        <v>62/45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>NE-5862</v>
+        <v>TLA S-19</v>
+      </c>
+      <c r="B61" t="str">
+        <v>TLA</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Titwala</v>
       </c>
       <c r="D61" t="str">
         <v>KYN-KSRA</v>
@@ -4622,13 +5219,16 @@
         <v>UP</v>
       </c>
       <c r="G61" t="str">
-        <v>58/31</v>
+        <v>63/03</v>
       </c>
       <c r="H61" t="str">
-        <v>Automatic</v>
+        <v>Manual</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
       </c>
       <c r="J61" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="K61" t="str">
         <v>Right</v>
@@ -4637,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -4661,21 +5261,33 @@
         <v>0</v>
       </c>
       <c r="U61">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V61">
         <v>1</v>
       </c>
+      <c r="W61" t="str">
+        <v/>
+      </c>
+      <c r="X61" t="str">
+        <v/>
+      </c>
       <c r="Y61">
-        <v>58.182</v>
+        <v>63.686</v>
       </c>
       <c r="Z61" t="str">
-        <v>58/31</v>
+        <v>63/03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>NE-5816</v>
+        <v>NE-6212</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
       </c>
       <c r="D62" t="str">
         <v>KYN-KSRA</v>
@@ -4687,16 +5299,19 @@
         <v>UP</v>
       </c>
       <c r="G62" t="str">
-        <v>58/07</v>
+        <v>62/29</v>
       </c>
       <c r="H62" t="str">
         <v>Automatic</v>
       </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
       <c r="J62" t="str">
         <v>Left</v>
       </c>
       <c r="K62" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -4726,21 +5341,33 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="V62">
         <v>1</v>
       </c>
+      <c r="W62" t="str">
+        <v/>
+      </c>
+      <c r="X62" t="str">
+        <v/>
+      </c>
       <c r="Y62">
-        <v>57.739000000000004</v>
+        <v>62.356</v>
       </c>
       <c r="Z62" t="str">
-        <v>58/07</v>
+        <v>62/29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>NE-5702</v>
+        <v>NE-6114</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
       </c>
       <c r="D63" t="str">
         <v>KYN-KSRA</v>
@@ -4752,11 +5379,14 @@
         <v>UP</v>
       </c>
       <c r="G63" t="str">
-        <v>57/01</v>
+        <v>61/31</v>
       </c>
       <c r="H63" t="str">
         <v>Automatic</v>
       </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
       <c r="J63" t="str">
         <v>Left</v>
       </c>
@@ -4791,21 +5421,33 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="V63">
         <v>1</v>
       </c>
+      <c r="W63" t="str">
+        <v/>
+      </c>
+      <c r="X63" t="str">
+        <v/>
+      </c>
       <c r="Y63">
-        <v>57.07</v>
+        <v>61.636</v>
       </c>
       <c r="Z63" t="str">
-        <v>57/01</v>
+        <v>61/31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>NE-5604</v>
+        <v>NE-6102</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
       </c>
       <c r="D64" t="str">
         <v>KYN-KSRA</v>
@@ -4817,16 +5459,19 @@
         <v>UP</v>
       </c>
       <c r="G64" t="str">
-        <v>56/05</v>
+        <v>61/05</v>
       </c>
       <c r="H64" t="str">
         <v>Automatic</v>
       </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
       <c r="J64" t="str">
         <v>Left</v>
       </c>
       <c r="K64" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -4856,21 +5501,33 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="V64">
         <v>1</v>
       </c>
+      <c r="W64" t="str">
+        <v/>
+      </c>
+      <c r="X64" t="str">
+        <v/>
+      </c>
       <c r="Y64">
-        <v>56.339</v>
+        <v>60.908</v>
       </c>
       <c r="Z64" t="str">
-        <v>56/05</v>
+        <v>61/05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>NE-5510</v>
+        <v>NE-6008</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
       </c>
       <c r="D65" t="str">
         <v>KYN-KSRA</v>
@@ -4882,11 +5539,14 @@
         <v>UP</v>
       </c>
       <c r="G65" t="str">
-        <v>55/27</v>
+        <v>60/15</v>
       </c>
       <c r="H65" t="str">
         <v>Automatic</v>
       </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
       <c r="J65" t="str">
         <v>Left</v>
       </c>
@@ -4926,22 +5586,28 @@
       <c r="V65">
         <v>1</v>
       </c>
+      <c r="W65" t="str">
+        <v/>
+      </c>
+      <c r="X65" t="str">
+        <v/>
+      </c>
       <c r="Y65">
-        <v>55.71</v>
+        <v>60.132</v>
       </c>
       <c r="Z65" t="str">
-        <v>55/27</v>
+        <v>60/15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>KYN S-78</v>
+        <v>Gate-48</v>
       </c>
       <c r="B66" t="str">
-        <v>KYN</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>Kalyan</v>
+        <v/>
       </c>
       <c r="D66" t="str">
         <v>KYN-KSRA</v>
@@ -4953,16 +5619,19 @@
         <v>UP</v>
       </c>
       <c r="G66" t="str">
-        <v>55/03</v>
+        <v>59/39</v>
       </c>
       <c r="H66" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
       </c>
       <c r="J66" t="str">
         <v>Left</v>
       </c>
       <c r="K66" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -4980,42 +5649,45 @@
         <v>0</v>
       </c>
       <c r="Q66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66">
         <v>0</v>
       </c>
       <c r="U66">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="V66">
         <v>1</v>
       </c>
+      <c r="W66" t="str">
+        <v/>
+      </c>
       <c r="X66" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
+        <v/>
       </c>
       <c r="Y66">
-        <v>54.895</v>
+        <v>59.375</v>
       </c>
       <c r="Z66" t="str">
-        <v>55/03</v>
+        <v>59/39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>KYN S-71</v>
+        <v>NE-5918</v>
       </c>
       <c r="B67" t="str">
-        <v>KYN</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>Kalyan</v>
+        <v/>
       </c>
       <c r="D67" t="str">
         <v>KYN-KSRA</v>
@@ -5027,13 +5699,16 @@
         <v>UP</v>
       </c>
       <c r="G67" t="str">
-        <v>54/1</v>
+        <v>59/07</v>
       </c>
       <c r="H67" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
       </c>
       <c r="J67" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="K67" t="str">
         <v>Left</v>
@@ -5042,10 +5717,10 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -5054,113 +5729,679 @@
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="V67">
         <v>1</v>
       </c>
+      <c r="W67" t="str">
+        <v/>
+      </c>
       <c r="X67" t="str">
-        <v>Book shows three left and one right arms on top of vertical stem</v>
+        <v/>
       </c>
       <c r="Y67">
-        <v>54.085</v>
+        <v>58.801</v>
       </c>
       <c r="Z67" t="str">
-        <v>54/1</v>
+        <v>59/07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
+        <v>NE-5862</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E68" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F68" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G68" t="str">
+        <v>58/31</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Automatic</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Right</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>500</v>
+      </c>
+      <c r="V68">
+        <v>1</v>
+      </c>
+      <c r="W68" t="str">
+        <v/>
+      </c>
+      <c r="X68" t="str">
+        <v/>
+      </c>
+      <c r="Y68">
+        <v>58.182</v>
+      </c>
+      <c r="Z68" t="str">
+        <v>58/31</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>NE-5816</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E69" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F69" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G69" t="str">
+        <v>58/07</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Automatic</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>500</v>
+      </c>
+      <c r="V69">
+        <v>1</v>
+      </c>
+      <c r="W69" t="str">
+        <v/>
+      </c>
+      <c r="X69" t="str">
+        <v/>
+      </c>
+      <c r="Y69">
+        <v>57.739000000000004</v>
+      </c>
+      <c r="Z69" t="str">
+        <v>58/07</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>NE-5702</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E70" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F70" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G70" t="str">
+        <v>57/01</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Automatic</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>250</v>
+      </c>
+      <c r="V70">
+        <v>1</v>
+      </c>
+      <c r="W70" t="str">
+        <v/>
+      </c>
+      <c r="X70" t="str">
+        <v/>
+      </c>
+      <c r="Y70">
+        <v>57.07</v>
+      </c>
+      <c r="Z70" t="str">
+        <v>57/01</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>NE-5604</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E71" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F71" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G71" t="str">
+        <v>56/05</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Automatic</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Right</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>220</v>
+      </c>
+      <c r="V71">
+        <v>1</v>
+      </c>
+      <c r="W71" t="str">
+        <v/>
+      </c>
+      <c r="X71" t="str">
+        <v/>
+      </c>
+      <c r="Y71">
+        <v>56.339</v>
+      </c>
+      <c r="Z71" t="str">
+        <v>56/05</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>NE-5510</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E72" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F72" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G72" t="str">
+        <v>55/27</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Automatic</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Right</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>300</v>
+      </c>
+      <c r="V72">
+        <v>1</v>
+      </c>
+      <c r="W72" t="str">
+        <v/>
+      </c>
+      <c r="X72" t="str">
+        <v/>
+      </c>
+      <c r="Y72">
+        <v>55.71</v>
+      </c>
+      <c r="Z72" t="str">
+        <v>55/27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>KYN S-78</v>
+      </c>
+      <c r="B73" t="str">
+        <v>KYN</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Kalyan</v>
+      </c>
+      <c r="D73" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E73" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F73" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G73" t="str">
+        <v>55/03</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Semi-Automatic</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>1</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="S73">
+        <v>1</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>350</v>
+      </c>
+      <c r="V73">
+        <v>1</v>
+      </c>
+      <c r="W73" t="str">
+        <v/>
+      </c>
+      <c r="X73" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
+      <c r="Y73">
+        <v>54.895</v>
+      </c>
+      <c r="Z73" t="str">
+        <v>55/03</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>KYN S-71</v>
+      </c>
+      <c r="B74" t="str">
+        <v>KYN</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Kalyan</v>
+      </c>
+      <c r="D74" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E74" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F74" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G74" t="str">
+        <v>54/1</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Semi-Automatic</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v>Left</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>1</v>
+      </c>
+      <c r="R74">
+        <v>1</v>
+      </c>
+      <c r="S74">
+        <v>3</v>
+      </c>
+      <c r="T74">
+        <v>1</v>
+      </c>
+      <c r="U74">
+        <v>280</v>
+      </c>
+      <c r="V74">
+        <v>1</v>
+      </c>
+      <c r="W74" t="str">
+        <v/>
+      </c>
+      <c r="X74" t="str">
+        <v>Book shows three left and one right arms on top of vertical stem</v>
+      </c>
+      <c r="Y74">
+        <v>54.085</v>
+      </c>
+      <c r="Z74" t="str">
+        <v>54/1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>KYN S-37</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B75" t="str">
         <v>KYN</v>
       </c>
-      <c r="C68" t="str">
+      <c r="C75" t="str">
         <v>Kalyan</v>
       </c>
-      <c r="D68" t="str">
-        <v>KYN-KSRA</v>
-      </c>
-      <c r="E68" t="str">
-        <v>UP NE</v>
-      </c>
-      <c r="F68" t="str">
-        <v>UP</v>
-      </c>
-      <c r="G68" t="str">
+      <c r="D75" t="str">
+        <v>KYN-KSRA</v>
+      </c>
+      <c r="E75" t="str">
+        <v>UP NE</v>
+      </c>
+      <c r="F75" t="str">
+        <v>UP</v>
+      </c>
+      <c r="G75" t="str">
         <v>PF-3 STR</v>
       </c>
-      <c r="H68" t="str">
+      <c r="H75" t="str">
         <v>Semi-Automatic</v>
       </c>
-      <c r="J68" t="str">
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
         <v>Right</v>
       </c>
-      <c r="K68" t="str">
+      <c r="K75" t="str">
         <v>Unknown</v>
       </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
         <v>200</v>
       </c>
-      <c r="V68">
-        <v>1</v>
-      </c>
-      <c r="W68" t="str">
+      <c r="V75">
+        <v>1</v>
+      </c>
+      <c r="W75" t="str">
         <v>RI:R1= S-19</v>
       </c>
-      <c r="X68" t="str">
+      <c r="X75" t="str">
         <v>Book shows one right arm on top of vertical stem</v>
       </c>
-      <c r="Y68">
+      <c r="Y75">
         <v>52.744</v>
       </c>
-      <c r="Z68" t="str">
+      <c r="Z75" t="str">
         <v>52/441</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z75"/>
   </ignoredErrors>
 </worksheet>
 </file>